--- a/Digital Chess Clock/Grading/1 stage/3-examples/Digital-Chess-Clock_Grading_1-stage_2026-02-28_3-examples_HumanGrading_Claude4.5SonnetGeneration.xlsx
+++ b/Digital Chess Clock/Grading/1 stage/3-examples/Digital-Chess-Clock_Grading_1-stage_2026-02-28_3-examples_HumanGrading_Claude4.5SonnetGeneration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/Digital Chess Clock/Grading/1 stage/3-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6024BF9-36F7-C147-9DCC-561C26E94A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BEA84E0-E2ED-CA4D-8F1D-0CAC372FFA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chess Clock" sheetId="1" r:id="rId1"/>
@@ -518,7 +518,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -809,11 +809,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -995,14 +1004,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1011,7 +1023,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="28">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1231,49 +1246,49 @@
   </dxfs>
   <tableStyles count="9">
     <tableStyle name="Chess Clock-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="26"/>
-      <tableStyleElement type="firstRowStripe" dxfId="25"/>
-      <tableStyleElement type="secondRowStripe" dxfId="24"/>
+      <tableStyleElement type="headerRow" dxfId="27"/>
+      <tableStyleElement type="firstRowStripe" dxfId="26"/>
+      <tableStyleElement type="secondRowStripe" dxfId="25"/>
     </tableStyle>
     <tableStyle name="Chess Clock Grader #1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="23"/>
-      <tableStyleElement type="firstRowStripe" dxfId="22"/>
-      <tableStyleElement type="secondRowStripe" dxfId="21"/>
+      <tableStyleElement type="headerRow" dxfId="24"/>
+      <tableStyleElement type="firstRowStripe" dxfId="23"/>
+      <tableStyleElement type="secondRowStripe" dxfId="22"/>
     </tableStyle>
     <tableStyle name="Chess Clock Grader #2-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="headerRow" dxfId="20"/>
-      <tableStyleElement type="firstRowStripe" dxfId="19"/>
-      <tableStyleElement type="secondRowStripe" dxfId="18"/>
+      <tableStyleElement type="headerRow" dxfId="21"/>
+      <tableStyleElement type="firstRowStripe" dxfId="20"/>
+      <tableStyleElement type="secondRowStripe" dxfId="19"/>
     </tableStyle>
     <tableStyle name="Metrics-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="secondRowStripe" dxfId="15"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="firstRowStripe" dxfId="17"/>
+      <tableStyleElement type="secondRowStripe" dxfId="16"/>
     </tableStyle>
     <tableStyle name="Metrics-style 2" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="headerRow" dxfId="14"/>
-      <tableStyleElement type="firstRowStripe" dxfId="13"/>
-      <tableStyleElement type="secondRowStripe" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
     <tableStyle name="Metrics-style 3" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="secondRowStripe" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="secondRowStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="Metrics-style 4" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="headerRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="secondRowStripe" dxfId="7"/>
     </tableStyle>
     <tableStyle name="Inter-rater-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
     <tableStyle name="Weighted Cohens Kappa-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1374,8 +1389,12 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Element"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Rater 1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Rater 2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Rater 1">
+      <calculatedColumnFormula>'Chess Clock Grader #1'!C2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Rater 2" dataDxfId="0">
+      <calculatedColumnFormula>'Chess Clock Grader #2'!C2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Weighted Cohens Kappa-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15523,16 +15542,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="76" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
       <c r="J1" s="24" t="s">
         <v>67</v>
       </c>
@@ -15854,16 +15873,16 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="25" t="s">
@@ -17185,17 +17204,17 @@
         <v>84</v>
       </c>
       <c r="E1" s="33"/>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="L1" s="77" t="s">
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="L1" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="str">
@@ -17465,17 +17484,17 @@
         <v>0.5</v>
       </c>
       <c r="E8" s="33"/>
-      <c r="F8" s="75" t="s">
+      <c r="F8" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
-      <c r="L8" s="77" t="s">
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="L8" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="M8" s="78"/>
-      <c r="N8" s="78"/>
+      <c r="M8" s="79"/>
+      <c r="N8" s="79"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="str">
@@ -17742,17 +17761,17 @@
         <v>1</v>
       </c>
       <c r="E15" s="33"/>
-      <c r="F15" s="75" t="s">
+      <c r="F15" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="G15" s="76"/>
-      <c r="H15" s="76"/>
-      <c r="I15" s="76"/>
-      <c r="L15" s="77" t="s">
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+      <c r="L15" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="M15" s="78"/>
-      <c r="N15" s="78"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="79"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="str">
@@ -18019,17 +18038,17 @@
         <v>0</v>
       </c>
       <c r="E22" s="33"/>
-      <c r="F22" s="75" t="s">
+      <c r="F22" s="74" t="s">
         <v>105</v>
       </c>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
-      <c r="I22" s="76"/>
-      <c r="L22" s="77" t="s">
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="75"/>
+      <c r="L22" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="M22" s="78"/>
-      <c r="N22" s="78"/>
+      <c r="M22" s="79"/>
+      <c r="N22" s="79"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="str">
@@ -18296,17 +18315,17 @@
         <v>0</v>
       </c>
       <c r="E29" s="33"/>
-      <c r="F29" s="75" t="s">
+      <c r="F29" s="74" t="s">
         <v>107</v>
       </c>
-      <c r="G29" s="76"/>
-      <c r="H29" s="76"/>
-      <c r="I29" s="76"/>
-      <c r="L29" s="77" t="s">
+      <c r="G29" s="75"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="75"/>
+      <c r="L29" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="M29" s="78"/>
-      <c r="N29" s="78"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="79"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="str">
@@ -18573,17 +18592,17 @@
         <v>0</v>
       </c>
       <c r="E36" s="33"/>
-      <c r="F36" s="75" t="s">
+      <c r="F36" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
-      <c r="I36" s="76"/>
-      <c r="L36" s="77" t="s">
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="75"/>
+      <c r="L36" s="78" t="s">
         <v>110</v>
       </c>
-      <c r="M36" s="78"/>
-      <c r="N36" s="78"/>
+      <c r="M36" s="79"/>
+      <c r="N36" s="79"/>
     </row>
     <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="str">
@@ -18850,17 +18869,17 @@
         <v>1</v>
       </c>
       <c r="E43" s="33"/>
-      <c r="F43" s="75" t="s">
+      <c r="F43" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="G43" s="76"/>
-      <c r="H43" s="76"/>
-      <c r="I43" s="76"/>
-      <c r="L43" s="77" t="s">
+      <c r="G43" s="75"/>
+      <c r="H43" s="75"/>
+      <c r="I43" s="75"/>
+      <c r="L43" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="M43" s="78"/>
-      <c r="N43" s="78"/>
+      <c r="M43" s="79"/>
+      <c r="N43" s="79"/>
     </row>
     <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="str">
@@ -19127,17 +19146,17 @@
         <v>0</v>
       </c>
       <c r="E50" s="33"/>
-      <c r="F50" s="75" t="s">
+      <c r="F50" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="G50" s="76"/>
-      <c r="H50" s="76"/>
-      <c r="I50" s="76"/>
-      <c r="L50" s="77" t="s">
+      <c r="G50" s="75"/>
+      <c r="H50" s="75"/>
+      <c r="I50" s="75"/>
+      <c r="L50" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="M50" s="78"/>
-      <c r="N50" s="78"/>
+      <c r="M50" s="79"/>
+      <c r="N50" s="79"/>
     </row>
     <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="str">
@@ -20389,6 +20408,12 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="L15:N15"/>
     <mergeCell ref="L22:N22"/>
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="L50:N50"/>
@@ -20399,12 +20424,6 @@
     <mergeCell ref="L36:N36"/>
     <mergeCell ref="F43:I43"/>
     <mergeCell ref="L43:N43"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="L15:N15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -20453,18 +20472,18 @@
         <v>84</v>
       </c>
       <c r="E1" s="33"/>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="L1" s="75" t="s">
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="L1" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
     </row>
     <row r="2" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="str">
@@ -20480,7 +20499,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="4">
-        <f>'Chess Clock Grader #1'!C2</f>
+        <f>'Chess Clock Grader #2'!C2</f>
         <v>1</v>
       </c>
       <c r="E2" s="33"/>
@@ -20550,7 +20569,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <f>'Chess Clock Grader #1'!C3</f>
+        <f>'Chess Clock Grader #2'!C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="33"/>
@@ -20559,15 +20578,15 @@
       </c>
       <c r="G3" s="41">
         <f>COUNTIFS($C$2:$C$90, $F3, $D$2:$D$90, G$2)</f>
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H3" s="42">
         <f>COUNTIFS($C$2:$C$46, $F3, $D$2:$D$46, H$2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="43">
         <f>COUNTIFS($C$2:$C$46, $F3, $D$2:$D$46, I$2)+MAX(D47-C47,0)+MAX(D48-C48,0)+MAX(D49-C49,0)+MAX(D50-C50,0)+MAX(D51-C51,0)+MAX(D52-C52,0)+MAX(D53-C53,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" ref="J3:J5" si="0">SUM(G3:I3)</f>
@@ -20595,11 +20614,11 @@
       </c>
       <c r="R3" s="41">
         <f t="shared" ref="R3:T3" si="2">($J3/$J$6) * (G$6/$J$6)</f>
-        <v>0.23113905325443787</v>
+        <v>0.20340236686390534</v>
       </c>
       <c r="S3" s="42">
         <f t="shared" si="2"/>
-        <v>4.6227810650887581E-2</v>
+        <v>7.3964497041420121E-2</v>
       </c>
       <c r="T3" s="43">
         <f t="shared" si="2"/>
@@ -20611,7 +20630,7 @@
       </c>
       <c r="W3" s="41">
         <f>SUMPRODUCT(G3:I5, M3:O5) /$J$6</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="X3" s="43" t="s">
         <v>117</v>
@@ -20631,7 +20650,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <f>'Chess Clock Grader #1'!C4</f>
+        <f>'Chess Clock Grader #2'!C4</f>
         <v>1</v>
       </c>
       <c r="E4" s="33"/>
@@ -20644,11 +20663,11 @@
       </c>
       <c r="H4" s="11">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" s="46">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="11">
         <f t="shared" si="0"/>
@@ -20676,11 +20695,11 @@
       </c>
       <c r="R4" s="45">
         <f t="shared" ref="R4:T4" si="5">($J4/$J$6) * (G$6/$J$6)</f>
-        <v>4.6227810650887581E-2</v>
+        <v>4.0680473372781065E-2</v>
       </c>
       <c r="S4" s="11">
         <f t="shared" si="5"/>
-        <v>9.2455621301775152E-3</v>
+        <v>1.4792899408284025E-2</v>
       </c>
       <c r="T4" s="46">
         <f t="shared" si="5"/>
@@ -20692,7 +20711,7 @@
       </c>
       <c r="W4" s="45">
         <f>SUMPRODUCT(R3:T5, M3:O5)</f>
-        <v>0.4937130177514793</v>
+        <v>0.49260355029585795</v>
       </c>
       <c r="X4" s="46" t="s">
         <v>119</v>
@@ -20712,7 +20731,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="4">
-        <f>'Chess Clock Grader #1'!C5</f>
+        <f>'Chess Clock Grader #2'!C5</f>
         <v>1</v>
       </c>
       <c r="E5" s="33"/>
@@ -20721,15 +20740,15 @@
       </c>
       <c r="G5" s="47">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, G$2)+MAX(C47-D47,0)+MAX(C48-D48,0)+MAX(C49-D49,0)+MAX(C50-D50,0)+MAX(C51-D51,0)+MAX(C52-D52,0)+MAX(C53-D53,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="48">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, H$2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" s="49">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, I$2)+ SUM(MIN(C47,D47), MIN(C48,D48), MIN(C49,D49), MIN(C50,D50), MIN(C51,D51), MIN(C52,D52), MIN(C53,D53))</f>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J5" s="11">
         <f t="shared" si="0"/>
@@ -20757,11 +20776,11 @@
       </c>
       <c r="R5" s="47">
         <f t="shared" ref="R5:T5" si="7">($J5/$J$6) * (G$6/$J$6)</f>
-        <v>0.20340236686390534</v>
+        <v>0.17899408284023668</v>
       </c>
       <c r="S5" s="48">
         <f t="shared" si="7"/>
-        <v>4.0680473372781065E-2</v>
+        <v>6.5088757396449703E-2</v>
       </c>
       <c r="T5" s="49">
         <f t="shared" si="7"/>
@@ -20773,7 +20792,7 @@
       </c>
       <c r="W5" s="47">
         <f>1-W3/W4</f>
-        <v>1</v>
+        <v>0.74624624624624625</v>
       </c>
       <c r="X5" s="49" t="s">
         <v>120</v>
@@ -20793,7 +20812,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <f>'Chess Clock Grader #1'!C6</f>
+        <f>'Chess Clock Grader #2'!C6</f>
         <v>1</v>
       </c>
       <c r="E6" s="33"/>
@@ -20802,11 +20821,11 @@
       </c>
       <c r="G6" s="11">
         <f t="shared" ref="G6:I6" si="8">SUM(G3:G5)</f>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H6" s="11">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="8"/>
@@ -20842,7 +20861,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="4">
-        <f>'Chess Clock Grader #1'!C7</f>
+        <f>'Chess Clock Grader #2'!C7</f>
         <v>1</v>
       </c>
       <c r="E7" s="33"/>
@@ -20864,16 +20883,16 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="4">
-        <f>'Chess Clock Grader #1'!C8</f>
+        <f>'Chess Clock Grader #2'!C8</f>
         <v>0.5</v>
       </c>
       <c r="E8" s="33"/>
-      <c r="F8" s="75" t="s">
+      <c r="F8" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="str">
@@ -20889,7 +20908,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <f>'Chess Clock Grader #1'!C9</f>
+        <f>'Chess Clock Grader #2'!C9</f>
         <v>0</v>
       </c>
       <c r="E9" s="33"/>
@@ -20959,7 +20978,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <f>'Chess Clock Grader #1'!C10</f>
+        <f>'Chess Clock Grader #2'!C10</f>
         <v>0</v>
       </c>
       <c r="E10" s="33"/>
@@ -20968,11 +20987,11 @@
       </c>
       <c r="G10" s="41">
         <f t="shared" ref="G10:H10" si="9">COUNTIFS($A$2:$A$90,$F$9,$C$2:$C$90,$F10,$D$2:$D$90,G$9)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H10" s="42">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" s="43">
         <f>COUNTIFS($A$2:$A$46,$F$9,$C$2:$C$46,$F10,$D$2:$D$46,I$9)+MAX(D47-C47,0)</f>
@@ -21004,15 +21023,15 @@
       </c>
       <c r="R10" s="41">
         <f t="shared" ref="R10:T10" si="12">($J10/$J$13) * (G$13/$J$13)</f>
-        <v>0.18367346938775508</v>
+        <v>0.12244897959183672</v>
       </c>
       <c r="S10" s="42">
         <f t="shared" si="12"/>
-        <v>3.0612244897959179E-2</v>
+        <v>6.1224489795918359E-2</v>
       </c>
       <c r="T10" s="43">
         <f t="shared" si="12"/>
-        <v>0.21428571428571427</v>
+        <v>0.24489795918367344</v>
       </c>
       <c r="U10" s="11"/>
       <c r="V10" s="44" t="s">
@@ -21020,7 +21039,7 @@
       </c>
       <c r="W10" s="41">
         <f>SUMPRODUCT(G10:I12, M10:O12) /$J$13</f>
-        <v>0</v>
+        <v>0.10714285714285714</v>
       </c>
       <c r="X10" s="43" t="s">
         <v>117</v>
@@ -21040,8 +21059,8 @@
         <v>0.5</v>
       </c>
       <c r="D11" s="4">
-        <f>'Chess Clock Grader #1'!C11</f>
-        <v>0.5</v>
+        <f>'Chess Clock Grader #2'!C11</f>
+        <v>1</v>
       </c>
       <c r="E11" s="33"/>
       <c r="F11" s="40">
@@ -21053,11 +21072,11 @@
       </c>
       <c r="H11" s="11">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="46">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="11">
         <f t="shared" si="10"/>
@@ -21085,15 +21104,15 @@
       </c>
       <c r="R11" s="45">
         <f t="shared" ref="R11:T11" si="15">($J11/$J$13) * (G$13/$J$13)</f>
-        <v>3.0612244897959179E-2</v>
+        <v>2.0408163265306121E-2</v>
       </c>
       <c r="S11" s="11">
         <f t="shared" si="15"/>
-        <v>5.1020408163265302E-3</v>
+        <v>1.020408163265306E-2</v>
       </c>
       <c r="T11" s="46">
         <f t="shared" si="15"/>
-        <v>3.5714285714285712E-2</v>
+        <v>4.0816326530612242E-2</v>
       </c>
       <c r="U11" s="11"/>
       <c r="V11" s="44" t="s">
@@ -21101,7 +21120,7 @@
       </c>
       <c r="W11" s="45">
         <f>SUMPRODUCT(R10:T12, M10:O12)</f>
-        <v>0.49489795918367346</v>
+        <v>0.48469387755102039</v>
       </c>
       <c r="X11" s="46" t="s">
         <v>119</v>
@@ -21121,8 +21140,8 @@
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <f>'Chess Clock Grader #1'!C12</f>
-        <v>0</v>
+        <f>'Chess Clock Grader #2'!C12</f>
+        <v>1</v>
       </c>
       <c r="E12" s="33"/>
       <c r="F12" s="40">
@@ -21166,15 +21185,15 @@
       </c>
       <c r="R12" s="47">
         <f t="shared" ref="R12:T12" si="17">($J12/$J$13) * (G$13/$J$13)</f>
-        <v>0.21428571428571427</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="S12" s="48">
         <f t="shared" si="17"/>
-        <v>3.5714285714285712E-2</v>
+        <v>7.1428571428571425E-2</v>
       </c>
       <c r="T12" s="49">
         <f t="shared" si="17"/>
-        <v>0.25</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="U12" s="11"/>
       <c r="V12" s="44" t="s">
@@ -21182,7 +21201,7 @@
       </c>
       <c r="W12" s="47">
         <f>1-W10/W11</f>
-        <v>1</v>
+        <v>0.77894736842105261</v>
       </c>
       <c r="X12" s="49" t="s">
         <v>120</v>
@@ -21202,8 +21221,8 @@
         <v>0</v>
       </c>
       <c r="D13" s="4">
-        <f>'Chess Clock Grader #1'!C13</f>
-        <v>0</v>
+        <f>'Chess Clock Grader #2'!C13</f>
+        <v>1</v>
       </c>
       <c r="E13" s="33"/>
       <c r="F13" s="50" t="s">
@@ -21211,15 +21230,15 @@
       </c>
       <c r="G13" s="11">
         <f t="shared" ref="G13:I13" si="18">SUM(G10:G12)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="11">
         <f t="shared" si="18"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13" s="11">
         <f>SUM(G10:I12)</f>
@@ -21240,8 +21259,8 @@
         <v>0.5</v>
       </c>
       <c r="D14" s="4">
-        <f>'Chess Clock Grader #1'!C14</f>
-        <v>0.5</v>
+        <f>'Chess Clock Grader #2'!C14</f>
+        <v>1</v>
       </c>
       <c r="E14" s="33"/>
     </row>
@@ -21259,16 +21278,16 @@
         <v>1</v>
       </c>
       <c r="D15" s="4">
-        <f>'Chess Clock Grader #1'!C15</f>
+        <f>'Chess Clock Grader #2'!C15</f>
         <v>1</v>
       </c>
       <c r="E15" s="33"/>
-      <c r="F15" s="75" t="s">
+      <c r="F15" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="G15" s="76"/>
-      <c r="H15" s="76"/>
-      <c r="I15" s="76"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="str">
@@ -21284,7 +21303,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="4">
-        <f>'Chess Clock Grader #1'!C16</f>
+        <f>'Chess Clock Grader #2'!C16</f>
         <v>0</v>
       </c>
       <c r="E16" s="33"/>
@@ -21354,7 +21373,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="4">
-        <f>'Chess Clock Grader #1'!C17</f>
+        <f>'Chess Clock Grader #2'!C17</f>
         <v>0</v>
       </c>
       <c r="E17" s="33"/>
@@ -21399,15 +21418,15 @@
       </c>
       <c r="R17" s="41">
         <f t="shared" ref="R17:T17" si="22">($J17/$J$20) * (G$20/$J$20)</f>
-        <v>7.1111111111111111E-2</v>
+        <v>8.8888888888888878E-2</v>
       </c>
       <c r="S17" s="42">
         <f t="shared" si="22"/>
-        <v>1.7777777777777778E-2</v>
+        <v>3.5555555555555556E-2</v>
       </c>
       <c r="T17" s="43">
         <f t="shared" si="22"/>
-        <v>0.17777777777777776</v>
+        <v>0.14222222222222222</v>
       </c>
       <c r="U17" s="11"/>
       <c r="V17" s="44" t="s">
@@ -21415,7 +21434,7 @@
       </c>
       <c r="W17" s="41">
         <f>SUMPRODUCT(G17:I19, M17:O19) /$J$20</f>
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="X17" s="43" t="s">
         <v>117</v>
@@ -21435,8 +21454,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="4">
-        <f>'Chess Clock Grader #1'!C18</f>
-        <v>0</v>
+        <f>'Chess Clock Grader #2'!C18</f>
+        <v>0.5</v>
       </c>
       <c r="E18" s="33"/>
       <c r="F18" s="40">
@@ -21448,11 +21467,11 @@
       </c>
       <c r="H18" s="11">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="46">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="11">
         <f t="shared" si="20"/>
@@ -21480,15 +21499,15 @@
       </c>
       <c r="R18" s="45">
         <f t="shared" ref="R18:T18" si="25">($J18/$J$20) * (G$20/$J$20)</f>
-        <v>1.7777777777777778E-2</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="S18" s="11">
         <f t="shared" si="25"/>
-        <v>4.4444444444444444E-3</v>
+        <v>8.8888888888888889E-3</v>
       </c>
       <c r="T18" s="46">
         <f t="shared" si="25"/>
-        <v>4.4444444444444439E-2</v>
+        <v>3.5555555555555556E-2</v>
       </c>
       <c r="U18" s="11"/>
       <c r="V18" s="44" t="s">
@@ -21496,7 +21515,7 @@
       </c>
       <c r="W18" s="45">
         <f>SUMPRODUCT(R17:T19, M17:O19)</f>
-        <v>0.41777777777777775</v>
+        <v>0.45555555555555555</v>
       </c>
       <c r="X18" s="46" t="s">
         <v>119</v>
@@ -21516,8 +21535,8 @@
         <v>0</v>
       </c>
       <c r="D19" s="4">
-        <f>'Chess Clock Grader #1'!C19</f>
-        <v>0</v>
+        <f>'Chess Clock Grader #2'!C19</f>
+        <v>0.5</v>
       </c>
       <c r="E19" s="33"/>
       <c r="F19" s="40">
@@ -21525,15 +21544,15 @@
       </c>
       <c r="G19" s="47">
         <f>COUNTIFS($A$2:$A$46,$F$16,$C$2:$C$46,$F19,$D$2:$D$46,G$16)+MAX(C48-D48,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="48">
         <f>COUNTIFS($A$2:$A$90,$F$16,$C$2:$C$90,$F19,$D$2:$D$90,H$16)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" s="49">
         <f>COUNTIFS($A$2:$A$46,$F$16,$C$2:$C$46,$F19,$D$2:$D$46,I$16) + MIN(C48,D48)</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J19" s="11">
         <f t="shared" si="20"/>
@@ -21561,15 +21580,15 @@
       </c>
       <c r="R19" s="47">
         <f t="shared" ref="R19:T19" si="27">($J19/$J$20) * (G$20/$J$20)</f>
-        <v>0.17777777777777776</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="S19" s="48">
         <f t="shared" si="27"/>
-        <v>4.4444444444444439E-2</v>
+        <v>8.8888888888888878E-2</v>
       </c>
       <c r="T19" s="49">
         <f t="shared" si="27"/>
-        <v>0.44444444444444442</v>
+        <v>0.35555555555555551</v>
       </c>
       <c r="U19" s="11"/>
       <c r="V19" s="44" t="s">
@@ -21577,7 +21596,7 @@
       </c>
       <c r="W19" s="47">
         <f>1-W17/W18</f>
-        <v>1</v>
+        <v>0.63414634146341464</v>
       </c>
       <c r="X19" s="49" t="s">
         <v>120</v>
@@ -21597,7 +21616,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="4">
-        <f>'Chess Clock Grader #1'!C20</f>
+        <f>'Chess Clock Grader #2'!C20</f>
         <v>0</v>
       </c>
       <c r="E20" s="33"/>
@@ -21606,15 +21625,15 @@
       </c>
       <c r="G20" s="11">
         <f t="shared" ref="G20:I20" si="28">SUM(G17:G19)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="11">
         <f t="shared" si="28"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J20" s="11">
         <f>SUM(G17:I19)</f>
@@ -21635,7 +21654,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="4">
-        <f>'Chess Clock Grader #1'!C21</f>
+        <f>'Chess Clock Grader #2'!C21</f>
         <v>0</v>
       </c>
       <c r="E21" s="33"/>
@@ -21654,16 +21673,16 @@
         <v>0</v>
       </c>
       <c r="D22" s="4">
-        <f>'Chess Clock Grader #1'!C22</f>
+        <f>'Chess Clock Grader #2'!C22</f>
         <v>0</v>
       </c>
       <c r="E22" s="33"/>
-      <c r="F22" s="75" t="s">
+      <c r="F22" s="74" t="s">
         <v>105</v>
       </c>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
-      <c r="I22" s="76"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="75"/>
     </row>
     <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="str">
@@ -21679,7 +21698,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="4">
-        <f>'Chess Clock Grader #1'!C23</f>
+        <f>'Chess Clock Grader #2'!C23</f>
         <v>1</v>
       </c>
       <c r="E23" s="33"/>
@@ -21749,7 +21768,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="4">
-        <f>'Chess Clock Grader #1'!C24</f>
+        <f>'Chess Clock Grader #2'!C24</f>
         <v>1</v>
       </c>
       <c r="E24" s="33"/>
@@ -21830,7 +21849,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="4">
-        <f>'Chess Clock Grader #1'!C25</f>
+        <f>'Chess Clock Grader #2'!C25</f>
         <v>1</v>
       </c>
       <c r="E25" s="33"/>
@@ -21911,7 +21930,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="4">
-        <f>'Chess Clock Grader #1'!C26</f>
+        <f>'Chess Clock Grader #2'!C26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33"/>
@@ -21992,7 +22011,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="4">
-        <f>'Chess Clock Grader #1'!C27</f>
+        <f>'Chess Clock Grader #2'!C27</f>
         <v>1</v>
       </c>
       <c r="E27" s="33"/>
@@ -22030,7 +22049,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="4">
-        <f>'Chess Clock Grader #1'!C28</f>
+        <f>'Chess Clock Grader #2'!C28</f>
         <v>0</v>
       </c>
       <c r="E28" s="33"/>
@@ -22049,16 +22068,16 @@
         <v>0</v>
       </c>
       <c r="D29" s="4">
-        <f>'Chess Clock Grader #1'!C29</f>
+        <f>'Chess Clock Grader #2'!C29</f>
         <v>0</v>
       </c>
       <c r="E29" s="33"/>
-      <c r="F29" s="75" t="s">
+      <c r="F29" s="74" t="s">
         <v>107</v>
       </c>
-      <c r="G29" s="76"/>
-      <c r="H29" s="76"/>
-      <c r="I29" s="76"/>
+      <c r="G29" s="75"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="75"/>
     </row>
     <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="str">
@@ -22074,7 +22093,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="4">
-        <f>'Chess Clock Grader #1'!C30</f>
+        <f>'Chess Clock Grader #2'!C30</f>
         <v>0</v>
       </c>
       <c r="E30" s="33"/>
@@ -22144,8 +22163,8 @@
         <v>1</v>
       </c>
       <c r="D31" s="4">
-        <f>'Chess Clock Grader #1'!C31</f>
-        <v>1</v>
+        <f>'Chess Clock Grader #2'!C31</f>
+        <v>0.5</v>
       </c>
       <c r="E31" s="33"/>
       <c r="F31" s="40">
@@ -22225,8 +22244,8 @@
         <v>1</v>
       </c>
       <c r="D32" s="4">
-        <f>'Chess Clock Grader #1'!C32</f>
-        <v>1</v>
+        <f>'Chess Clock Grader #2'!C32</f>
+        <v>0.5</v>
       </c>
       <c r="E32" s="33"/>
       <c r="F32" s="40">
@@ -22306,7 +22325,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="4">
-        <f>'Chess Clock Grader #1'!C33</f>
+        <f>'Chess Clock Grader #2'!C33</f>
         <v>1</v>
       </c>
       <c r="E33" s="33"/>
@@ -22387,7 +22406,7 @@
         <v>0.5</v>
       </c>
       <c r="D34" s="4">
-        <f>'Chess Clock Grader #1'!C34</f>
+        <f>'Chess Clock Grader #2'!C34</f>
         <v>0.5</v>
       </c>
       <c r="E34" s="33"/>
@@ -22425,7 +22444,7 @@
         <v>0.5</v>
       </c>
       <c r="D35" s="4">
-        <f>'Chess Clock Grader #1'!C35</f>
+        <f>'Chess Clock Grader #2'!C35</f>
         <v>0.5</v>
       </c>
       <c r="E35" s="33"/>
@@ -22444,16 +22463,16 @@
         <v>0</v>
       </c>
       <c r="D36" s="4">
-        <f>'Chess Clock Grader #1'!C36</f>
+        <f>'Chess Clock Grader #2'!C36</f>
         <v>0</v>
       </c>
       <c r="E36" s="33"/>
-      <c r="F36" s="75" t="s">
+      <c r="F36" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
-      <c r="I36" s="76"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="75"/>
     </row>
     <row r="37" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="str">
@@ -22469,7 +22488,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="4">
-        <f>'Chess Clock Grader #1'!C37</f>
+        <f>'Chess Clock Grader #2'!C37</f>
         <v>1</v>
       </c>
       <c r="E37" s="33"/>
@@ -22539,8 +22558,8 @@
         <v>1</v>
       </c>
       <c r="D38" s="4">
-        <f>'Chess Clock Grader #1'!C38</f>
-        <v>1</v>
+        <f>'Chess Clock Grader #2'!C38</f>
+        <v>0.5</v>
       </c>
       <c r="E38" s="33"/>
       <c r="F38" s="40">
@@ -22548,7 +22567,7 @@
       </c>
       <c r="G38" s="41">
         <f t="shared" ref="G38:H38" si="49">COUNTIFS($A$2:$A$90,$F$37,$C$2:$C$90,$F38,$D$2:$D$90,G$37)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H38" s="42">
         <f t="shared" si="49"/>
@@ -22556,7 +22575,7 @@
       </c>
       <c r="I38" s="43">
         <f>COUNTIFS($A$2:$A$46,$F$37,$C$2:$C$46,$F38,$D$2:$D$46,I$37)+MAX(D50-C50,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38" s="11">
         <f t="shared" ref="J38:J40" si="50">SUM(G38:I38)</f>
@@ -22584,15 +22603,15 @@
       </c>
       <c r="R38" s="65">
         <f t="shared" ref="R38:T38" si="52">($J38/$J$41) * (G$41/$J$41)</f>
-        <v>0.30864197530864201</v>
+        <v>0.18518518518518517</v>
       </c>
       <c r="S38" s="66">
         <f t="shared" si="52"/>
-        <v>0.12345679012345678</v>
+        <v>0.18518518518518517</v>
       </c>
       <c r="T38" s="67">
         <f t="shared" si="52"/>
-        <v>0.12345679012345678</v>
+        <v>0.18518518518518517</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="44" t="s">
@@ -22600,7 +22619,7 @@
       </c>
       <c r="W38" s="41">
         <f>SUMPRODUCT(G38:I40, M38:O40) /$J$41</f>
-        <v>0</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="X38" s="43" t="s">
         <v>117</v>
@@ -22620,7 +22639,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="4">
-        <f>'Chess Clock Grader #1'!C39</f>
+        <f>'Chess Clock Grader #2'!C39</f>
         <v>1</v>
       </c>
       <c r="E39" s="33"/>
@@ -22665,15 +22684,15 @@
       </c>
       <c r="R39" s="68">
         <f t="shared" ref="R39:T39" si="55">($J39/$J$41) * (G$41/$J$41)</f>
-        <v>0.12345679012345678</v>
+        <v>7.407407407407407E-2</v>
       </c>
       <c r="S39" s="62">
         <f t="shared" si="55"/>
-        <v>4.9382716049382713E-2</v>
+        <v>7.407407407407407E-2</v>
       </c>
       <c r="T39" s="69">
         <f t="shared" si="55"/>
-        <v>4.9382716049382713E-2</v>
+        <v>7.407407407407407E-2</v>
       </c>
       <c r="U39" s="11"/>
       <c r="V39" s="44" t="s">
@@ -22681,7 +22700,7 @@
       </c>
       <c r="W39" s="45">
         <f>SUMPRODUCT(R38:T40, M38:O40)</f>
-        <v>0.41975308641975306</v>
+        <v>0.46296296296296297</v>
       </c>
       <c r="X39" s="46" t="s">
         <v>119</v>
@@ -22701,8 +22720,8 @@
         <v>1</v>
       </c>
       <c r="D40" s="4">
-        <f>'Chess Clock Grader #1'!C40</f>
-        <v>1</v>
+        <f>'Chess Clock Grader #2'!C40</f>
+        <v>0</v>
       </c>
       <c r="E40" s="33"/>
       <c r="F40" s="40">
@@ -22714,11 +22733,11 @@
       </c>
       <c r="H40" s="48">
         <f>COUNTIFS($A$2:$A$90,$F$37,$C$2:$C$90,$F40,$D$2:$D$90,H$37)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="49">
         <f>COUNTIFS($A$2:$A$46,$F$37,$C$2:$C$46,$F40,$D$2:$D$46,I$37) + MIN(C50,D50)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="11">
         <f t="shared" si="50"/>
@@ -22746,15 +22765,15 @@
       </c>
       <c r="R40" s="70">
         <f t="shared" ref="R40:T40" si="57">($J40/$J$41) * (G$41/$J$41)</f>
-        <v>0.12345679012345678</v>
+        <v>7.407407407407407E-2</v>
       </c>
       <c r="S40" s="71">
         <f t="shared" si="57"/>
-        <v>4.9382716049382713E-2</v>
+        <v>7.407407407407407E-2</v>
       </c>
       <c r="T40" s="72">
         <f t="shared" si="57"/>
-        <v>4.9382716049382713E-2</v>
+        <v>7.407407407407407E-2</v>
       </c>
       <c r="U40" s="11"/>
       <c r="V40" s="44" t="s">
@@ -22762,7 +22781,7 @@
       </c>
       <c r="W40" s="47">
         <f>1-W38/W39</f>
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="X40" s="49" t="s">
         <v>120</v>
@@ -22782,7 +22801,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="4">
-        <f>'Chess Clock Grader #1'!C41</f>
+        <f>'Chess Clock Grader #2'!C41</f>
         <v>0</v>
       </c>
       <c r="E41" s="33"/>
@@ -22791,15 +22810,15 @@
       </c>
       <c r="G41" s="11">
         <f t="shared" ref="G41:I41" si="58">SUM(G38:G40)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H41" s="11">
         <f t="shared" si="58"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I41" s="11">
         <f t="shared" si="58"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J41" s="11">
         <f>SUM(G38:I40)</f>
@@ -22820,7 +22839,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="4">
-        <f>'Chess Clock Grader #1'!C42</f>
+        <f>'Chess Clock Grader #2'!C42</f>
         <v>0</v>
       </c>
       <c r="E42" s="33"/>
@@ -22839,16 +22858,16 @@
         <v>1</v>
       </c>
       <c r="D43" s="4">
-        <f>'Chess Clock Grader #1'!C43</f>
+        <f>'Chess Clock Grader #2'!C43</f>
         <v>1</v>
       </c>
       <c r="E43" s="33"/>
-      <c r="F43" s="75" t="s">
+      <c r="F43" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="G43" s="76"/>
-      <c r="H43" s="76"/>
-      <c r="I43" s="76"/>
+      <c r="G43" s="75"/>
+      <c r="H43" s="75"/>
+      <c r="I43" s="75"/>
     </row>
     <row r="44" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="str">
@@ -22864,7 +22883,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="4">
-        <f>'Chess Clock Grader #1'!C44</f>
+        <f>'Chess Clock Grader #2'!C44</f>
         <v>1</v>
       </c>
       <c r="E44" s="33"/>
@@ -22934,7 +22953,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="4">
-        <f>'Chess Clock Grader #1'!C45</f>
+        <f>'Chess Clock Grader #2'!C45</f>
         <v>0</v>
       </c>
       <c r="E45" s="33"/>
@@ -23010,12 +23029,12 @@
         <f>'Chess Clock Grader #1'!B46</f>
         <v>on =&gt; off</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="73">
         <f>'Chess Clock Grader #1'!C46</f>
         <v>1</v>
       </c>
-      <c r="D46" s="54">
-        <f>'Chess Clock Grader #1'!C46</f>
+      <c r="D46" s="73">
+        <f>'Chess Clock Grader #2'!C46</f>
         <v>1</v>
       </c>
       <c r="E46" s="33"/>
@@ -23091,12 +23110,12 @@
         <f>'Chess Clock Grader #1'!B47</f>
         <v>additional elements</v>
       </c>
-      <c r="C47" s="56">
+      <c r="C47" s="4">
         <f>'Chess Clock Grader #1'!C47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="57">
-        <f>'Chess Clock Grader #1'!C47</f>
+      <c r="D47" s="4">
+        <f>'Chess Clock Grader #2'!C47</f>
         <v>0</v>
       </c>
       <c r="E47" s="33"/>
@@ -23172,12 +23191,12 @@
         <f>'Chess Clock Grader #1'!B48</f>
         <v>additional elements</v>
       </c>
-      <c r="C48" s="17">
+      <c r="C48" s="4">
         <f>'Chess Clock Grader #1'!C48</f>
         <v>0</v>
       </c>
-      <c r="D48" s="59">
-        <f>'Chess Clock Grader #1'!C48</f>
+      <c r="D48" s="4">
+        <f>'Chess Clock Grader #2'!C48</f>
         <v>0</v>
       </c>
       <c r="E48" s="33"/>
@@ -23210,12 +23229,12 @@
         <f>'Chess Clock Grader #1'!B49</f>
         <v>additional elements</v>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="4">
         <f>'Chess Clock Grader #1'!C49</f>
         <v>0</v>
       </c>
-      <c r="D49" s="59">
-        <f>'Chess Clock Grader #1'!C49</f>
+      <c r="D49" s="4">
+        <f>'Chess Clock Grader #2'!C49</f>
         <v>0</v>
       </c>
       <c r="E49" s="33"/>
@@ -23229,21 +23248,21 @@
         <f>'Chess Clock Grader #1'!B50</f>
         <v>additional elements</v>
       </c>
-      <c r="C50" s="17">
+      <c r="C50" s="4">
         <f>'Chess Clock Grader #1'!C50</f>
         <v>0</v>
       </c>
-      <c r="D50" s="59">
-        <f>'Chess Clock Grader #1'!C50</f>
+      <c r="D50" s="4">
+        <f>'Chess Clock Grader #2'!C50</f>
         <v>0</v>
       </c>
       <c r="E50" s="33"/>
-      <c r="F50" s="75" t="s">
+      <c r="F50" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="G50" s="76"/>
-      <c r="H50" s="76"/>
-      <c r="I50" s="76"/>
+      <c r="G50" s="75"/>
+      <c r="H50" s="75"/>
+      <c r="I50" s="75"/>
     </row>
     <row r="51" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="str">
@@ -23254,12 +23273,12 @@
         <f>'Chess Clock Grader #1'!B51</f>
         <v>additional elements</v>
       </c>
-      <c r="C51" s="17">
+      <c r="C51" s="4">
         <f>'Chess Clock Grader #1'!C51</f>
         <v>0</v>
       </c>
-      <c r="D51" s="59">
-        <f>'Chess Clock Grader #1'!C51</f>
+      <c r="D51" s="4">
+        <f>'Chess Clock Grader #2'!C51</f>
         <v>0</v>
       </c>
       <c r="E51" s="33"/>
@@ -23324,12 +23343,12 @@
         <f>'Chess Clock Grader #1'!B52</f>
         <v>additional elements</v>
       </c>
-      <c r="C52" s="17">
+      <c r="C52" s="4">
         <f>'Chess Clock Grader #1'!C52</f>
         <v>0</v>
       </c>
-      <c r="D52" s="59">
-        <f>'Chess Clock Grader #1'!C52</f>
+      <c r="D52" s="4">
+        <f>'Chess Clock Grader #2'!C52</f>
         <v>0</v>
       </c>
       <c r="E52" s="33"/>
@@ -23405,12 +23424,12 @@
         <f>'Chess Clock Grader #1'!B53</f>
         <v>additional elements</v>
       </c>
-      <c r="C53" s="17">
+      <c r="C53" s="4">
         <f>'Chess Clock Grader #1'!C53</f>
         <v>0</v>
       </c>
-      <c r="D53" s="59">
-        <f>'Chess Clock Grader #1'!C53</f>
+      <c r="D53" s="4">
+        <f>'Chess Clock Grader #2'!C53</f>
         <v>0</v>
       </c>
       <c r="E53" s="33"/>
